--- a/artfynd/A 32309-2022 artfynd.xlsx
+++ b/artfynd/A 32309-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135793822</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>135793655</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>135793686</v>
       </c>
       <c r="B4" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>135793730</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>135793893</v>
       </c>
       <c r="B6" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135793931</v>
       </c>
       <c r="B7" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135794026</v>
       </c>
       <c r="B8" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>135794185</v>
       </c>
       <c r="B9" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>135794359</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>135794479</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135794622</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 32309-2022 artfynd.xlsx
+++ b/artfynd/A 32309-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135793822</v>
       </c>
       <c r="B2" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>135793655</v>
       </c>
       <c r="B3" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>135793686</v>
       </c>
       <c r="B4" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>135793730</v>
       </c>
       <c r="B5" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>135793893</v>
       </c>
       <c r="B6" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135793931</v>
       </c>
       <c r="B7" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135794026</v>
       </c>
       <c r="B8" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>135794185</v>
       </c>
       <c r="B9" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>135794359</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>135794479</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135794622</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 32309-2022 artfynd.xlsx
+++ b/artfynd/A 32309-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135793822</v>
       </c>
       <c r="B2" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>135793655</v>
       </c>
       <c r="B3" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>135793686</v>
       </c>
       <c r="B4" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>135793730</v>
       </c>
       <c r="B5" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>135793893</v>
       </c>
       <c r="B6" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135793931</v>
       </c>
       <c r="B7" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135794026</v>
       </c>
       <c r="B8" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>135794185</v>
       </c>
       <c r="B9" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>135794359</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>135794479</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135794622</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 32309-2022 artfynd.xlsx
+++ b/artfynd/A 32309-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135793822</v>
       </c>
       <c r="B2" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>135793655</v>
       </c>
       <c r="B3" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>135793686</v>
       </c>
       <c r="B4" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>135793730</v>
       </c>
       <c r="B5" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>135793893</v>
       </c>
       <c r="B6" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135793931</v>
       </c>
       <c r="B7" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135794026</v>
       </c>
       <c r="B8" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>135794185</v>
       </c>
       <c r="B9" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>135794359</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>135794479</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135794622</v>
       </c>
       <c r="B12" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
